--- a/E/PROPEM.xlsx
+++ b/E/PROPEM.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="68" uniqueCount="35">
   <si>
     <t/>
   </si>
@@ -508,7 +508,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F11"/>
+  <dimension ref="A1:H11"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -516,10 +516,11 @@
     <col min="3" max="3" width="8" customWidth="1"/>
     <col min="4" max="4" width="3" customWidth="1"/>
     <col min="5" max="5" width="4" customWidth="1"/>
-    <col min="6" max="6" width="11" customWidth="1"/>
+    <col min="6" max="7" width="10" customWidth="1"/>
+    <col min="8" max="8" width="11" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -538,8 +539,14 @@
       <c r="F1" s="1" t="s">
         <v>0</v>
       </c>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
@@ -555,11 +562,11 @@
       <c r="E2" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F2" s="1" t="s">
+      <c r="H2" s="1" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>6</v>
       </c>
@@ -575,11 +582,11 @@
       <c r="E3" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="F3" s="1" t="s">
+      <c r="H3" s="1" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
         <v>9</v>
       </c>
@@ -595,11 +602,11 @@
       <c r="E4" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F4" s="1" t="s">
+      <c r="H4" s="1" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
         <v>12</v>
       </c>
@@ -615,11 +622,11 @@
       <c r="E5" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="F5" s="1" t="s">
+      <c r="H5" s="1" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
         <v>15</v>
       </c>
@@ -635,11 +642,11 @@
       <c r="E6" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="F6" s="1" t="s">
+      <c r="H6" s="1" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
         <v>17</v>
       </c>
@@ -655,11 +662,11 @@
       <c r="E7" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="F7" s="1" t="s">
+      <c r="H7" s="1" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
         <v>21</v>
       </c>
@@ -675,11 +682,11 @@
       <c r="E8" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="F8" s="1" t="s">
+      <c r="H8" s="1" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
         <v>24</v>
       </c>
@@ -695,11 +702,11 @@
       <c r="E9" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="F9" s="1" t="s">
+      <c r="H9" s="1" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
         <v>27</v>
       </c>
@@ -715,11 +722,11 @@
       <c r="E10" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="F10" s="1" t="s">
+      <c r="H10" s="1" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
         <v>31</v>
       </c>
@@ -735,7 +742,7 @@
       <c r="E11" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="F11" s="1" t="s">
+      <c r="H11" s="1" t="s">
         <v>34</v>
       </c>
     </row>

--- a/E/PROPEM.xlsx
+++ b/E/PROPEM.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="68" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="35">
   <si>
     <t/>
   </si>
@@ -508,7 +508,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H11"/>
+  <dimension ref="A1:F11"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -516,11 +516,10 @@
     <col min="3" max="3" width="8" customWidth="1"/>
     <col min="4" max="4" width="3" customWidth="1"/>
     <col min="5" max="5" width="4" customWidth="1"/>
-    <col min="6" max="7" width="10" customWidth="1"/>
-    <col min="8" max="8" width="11" customWidth="1"/>
+    <col min="6" max="6" width="11" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -539,14 +538,8 @@
       <c r="F1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="G1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
@@ -562,11 +555,11 @@
       <c r="E2" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="H2" s="1" t="s">
+      <c r="F2" s="1" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>6</v>
       </c>
@@ -582,11 +575,11 @@
       <c r="E3" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="H3" s="1" t="s">
+      <c r="F3" s="1" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
         <v>9</v>
       </c>
@@ -602,11 +595,11 @@
       <c r="E4" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="H4" s="1" t="s">
+      <c r="F4" s="1" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
         <v>12</v>
       </c>
@@ -622,11 +615,11 @@
       <c r="E5" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="H5" s="1" t="s">
+      <c r="F5" s="1" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
         <v>15</v>
       </c>
@@ -642,11 +635,11 @@
       <c r="E6" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="H6" s="1" t="s">
+      <c r="F6" s="1" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
         <v>17</v>
       </c>
@@ -662,11 +655,11 @@
       <c r="E7" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="H7" s="1" t="s">
+      <c r="F7" s="1" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
         <v>21</v>
       </c>
@@ -682,11 +675,11 @@
       <c r="E8" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="H8" s="1" t="s">
+      <c r="F8" s="1" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
         <v>24</v>
       </c>
@@ -702,11 +695,11 @@
       <c r="E9" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="H9" s="1" t="s">
+      <c r="F9" s="1" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
         <v>27</v>
       </c>
@@ -722,11 +715,11 @@
       <c r="E10" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="H10" s="1" t="s">
+      <c r="F10" s="1" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
         <v>31</v>
       </c>
@@ -742,7 +735,7 @@
       <c r="E11" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="H11" s="1" t="s">
+      <c r="F11" s="1" t="s">
         <v>34</v>
       </c>
     </row>
